--- a/Supporting documentation/institutional_systemic_risk_assessments_supporting_material.xlsx
+++ b/Supporting documentation/institutional_systemic_risk_assessments_supporting_material.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kvase0-my.sharepoint.com/personal/loudel30_kva_se/Documents/Dokument/GitHub/systemic-risks-assessments/Supporting documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{D15DA587-4025-44E2-8014-9ACD4C5F2BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{493FEBDC-1172-4E87-A809-2148D6EDE5E3}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{D15DA587-4025-44E2-8014-9ACD4C5F2BC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07B7659A-5793-4C42-B65E-D09C0815B22A}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary table" sheetId="1" r:id="rId1"/>
@@ -1022,7 +1022,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>19</v>
@@ -1098,7 +1098,7 @@
         <v>19</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>19</v>
